--- a/CU-Batch4-Dotnet-6973825-ShreyaBiswas.xlsx
+++ b/CU-Batch4-Dotnet-6973825-ShreyaBiswas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4fdb74b276362dfa/Pictures/Documents/Capgemini Training/CU-DotNet-Jan26-B4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{1C29B338-BF50-4A44-B2C5-1A7A5E10CE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9422895-1884-42A2-B34B-A647AC7C1A33}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{1C29B338-BF50-4A44-B2C5-1A7A5E10CE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5337916-69B9-41A3-9D89-4794170D6F23}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C99DFE55-A9F3-4CE7-8732-71313EE2B406}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="78">
   <si>
     <t>SNO</t>
   </si>
@@ -262,6 +262,12 @@
   </si>
   <si>
     <t>https://github.com/shreyaBISWAS10/CU-DotNet-Jan26-B4/tree/main/Week6/Day31</t>
+  </si>
+  <si>
+    <t>https://github.com/shreyaBISWAS10/CU-DotNet-Jan26-B4/tree/main/Week8/Day43</t>
+  </si>
+  <si>
+    <t>https://github.com/shreyaBISWAS10/CU-DotNet-Jan26-B4/tree/main/Week8/Day44</t>
   </si>
 </sst>
 </file>
@@ -1072,6 +1078,9 @@
       <c r="B38" t="s">
         <v>29</v>
       </c>
+      <c r="C38" s="3" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
@@ -1079,6 +1088,9 @@
       </c>
       <c r="B39" t="s">
         <v>30</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -1130,6 +1142,8 @@
     <hyperlink ref="C5" r:id="rId34" xr:uid="{4DA25F6C-CEC7-4361-950B-4F9250353309}"/>
     <hyperlink ref="C4" r:id="rId35" xr:uid="{0CC1D889-856D-442A-91C7-0131FB3F23E3}"/>
     <hyperlink ref="C23" r:id="rId36" xr:uid="{5383BB0A-8EBD-47D6-82BD-A76489B2F117}"/>
+    <hyperlink ref="C38" r:id="rId37" xr:uid="{275413BA-26EC-4FD5-8925-FA3C338BD8F5}"/>
+    <hyperlink ref="C39" r:id="rId38" xr:uid="{981309F1-6167-46BD-B642-1850A3A59235}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CU-Batch4-Dotnet-6973825-ShreyaBiswas.xlsx
+++ b/CU-Batch4-Dotnet-6973825-ShreyaBiswas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4fdb74b276362dfa/Pictures/Documents/Capgemini Training/CU-DotNet-Jan26-B4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{1C29B338-BF50-4A44-B2C5-1A7A5E10CE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5337916-69B9-41A3-9D89-4794170D6F23}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{1C29B338-BF50-4A44-B2C5-1A7A5E10CE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10CF51DF-FE84-45C2-9BD7-2D44E46E4F2E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C99DFE55-A9F3-4CE7-8732-71313EE2B406}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="82">
   <si>
     <t>SNO</t>
   </si>
@@ -268,6 +268,18 @@
   </si>
   <si>
     <t>https://github.com/shreyaBISWAS10/CU-DotNet-Jan26-B4/tree/main/Week8/Day44</t>
+  </si>
+  <si>
+    <t>https://github.com/shreyaBISWAS10/CU-DotNet-Jan26-B4/tree/main/Week9/Day47</t>
+  </si>
+  <si>
+    <t>Day47-01-Cargo</t>
+  </si>
+  <si>
+    <t>https://github.com/shreyaBISWAS10/CU-DotNet-Jan26-B4/tree/main/Week9/Day48</t>
+  </si>
+  <si>
+    <t>Day48-01-EntryWebForm</t>
   </si>
 </sst>
 </file>
@@ -1097,10 +1109,22 @@
       <c r="A40" s="1">
         <v>39</v>
       </c>
+      <c r="B40" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/CU-Batch4-Dotnet-6973825-ShreyaBiswas.xlsx
+++ b/CU-Batch4-Dotnet-6973825-ShreyaBiswas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4fdb74b276362dfa/Pictures/Documents/Capgemini Training/CU-DotNet-Jan26-B4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{1C29B338-BF50-4A44-B2C5-1A7A5E10CE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10CF51DF-FE84-45C2-9BD7-2D44E46E4F2E}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{1C29B338-BF50-4A44-B2C5-1A7A5E10CE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3FFDE7B-E59A-49FB-8DD1-077E8A2D0D04}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C99DFE55-A9F3-4CE7-8732-71313EE2B406}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="86">
   <si>
     <t>SNO</t>
   </si>
@@ -280,6 +280,18 @@
   </si>
   <si>
     <t>Day48-01-EntryWebForm</t>
+  </si>
+  <si>
+    <t>https://github.com/shreyaBISWAS10/CU-DotNet-Jan26-B4/tree/main/Week9/Day50</t>
+  </si>
+  <si>
+    <t>https://github.com/shreyaBISWAS10/CU-DotNet-Jan26-B4/tree/main/Week9/Day51</t>
+  </si>
+  <si>
+    <t>Day51-01-StreamCollection</t>
+  </si>
+  <si>
+    <t>Day50-01-StudentsDictionary</t>
   </si>
 </sst>
 </file>
@@ -664,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E48ED98-B4C9-4546-A948-8E03A0929C33}">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="1"/>
@@ -1125,6 +1137,28 @@
       </c>
       <c r="C41" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
